--- a/api/templates/export/contacts/fr.xlsx
+++ b/api/templates/export/contacts/fr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10420"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/export/contacts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/export/contacts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C401531-C11A-A148-88CC-B6E77C2B1018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AA3928-1D71-7B41-8DD3-E2C66F68B7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17500" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>&lt;level&gt;</t>
-  </si>
-  <si>
     <t>&lt;state&gt;</t>
   </si>
   <si>
@@ -64,6 +61,27 @@
   </si>
   <si>
     <t>Étiquettes</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Téléphone</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>&lt;assignments&gt;</t>
+  </si>
+  <si>
+    <t>&lt;email&gt;</t>
+  </si>
+  <si>
+    <t>&lt;cell&gt;</t>
+  </si>
+  <si>
+    <t>&lt;phone&gt;</t>
   </si>
 </sst>
 </file>
@@ -136,7 +154,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -154,7 +172,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -169,7 +187,22 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -181,9 +214,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -196,9 +227,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -250,39 +279,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -694,69 +726,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.5" style="7" customWidth="1"/>
-    <col min="2" max="2" width="33.1640625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="26" style="2" customWidth="1"/>
-    <col min="5" max="5" width="34" style="2" customWidth="1"/>
+    <col min="1" max="1" width="53.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="33.1640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" customWidth="1"/>
+    <col min="7" max="8" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="B5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>5</v>
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/api/templates/export/contacts/fr.xlsx
+++ b/api/templates/export/contacts/fr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/export/contacts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AA3928-1D71-7B41-8DD3-E2C66F68B7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F996A1-AC92-1C4C-B1AC-1D5A04B14E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17500" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>&lt;name&gt;</t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>&lt;phone&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lastLogin&gt;</t>
+  </si>
+  <si>
+    <t>Dernier login</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="53.5" style="4" customWidth="1"/>
@@ -735,25 +741,26 @@
     <col min="5" max="5" width="34" style="1" customWidth="1"/>
     <col min="6" max="6" width="28.6640625" customWidth="1"/>
     <col min="7" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -775,11 +782,14 @@
       <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="I5" s="8" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>0</v>
       </c>
@@ -804,8 +814,11 @@
       <c r="H6" s="12" t="s">
         <v>18</v>
       </c>
+      <c r="I6" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
